--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_OV_Fiets.xlsx
@@ -388,13 +388,13 @@
         <v>17534.69286527517</v>
       </c>
       <c r="C2">
-        <v>37428.36890565915</v>
+        <v>37428.4701772776</v>
       </c>
       <c r="D2">
-        <v>72940.47656631895</v>
+        <v>72941.24805892342</v>
       </c>
       <c r="E2">
-        <v>110420.1622308842</v>
+        <v>110420.7198664097</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>180330.6679746063</v>
+        <v>180331.0875237142</v>
       </c>
       <c r="C3">
-        <v>335386.9156849797</v>
+        <v>335390.1000186463</v>
       </c>
       <c r="D3">
-        <v>407095.7643066295</v>
+        <v>407105.6389427788</v>
       </c>
       <c r="E3">
-        <v>452977.2437251885</v>
+        <v>452986.4132099262</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19667.09567762947</v>
+        <v>19667.22160216517</v>
       </c>
       <c r="C4">
-        <v>37369.10151870131</v>
+        <v>37369.8883905115</v>
       </c>
       <c r="D4">
-        <v>59618.34529532547</v>
+        <v>59623.53284766401</v>
       </c>
       <c r="E4">
-        <v>77206.95400038443</v>
+        <v>77210.15693260368</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -456,13 +456,13 @@
         <v>105936.6863591248</v>
       </c>
       <c r="C6">
-        <v>135014.8700967542</v>
+        <v>135015.3277845521</v>
       </c>
       <c r="D6">
-        <v>124254.8461279849</v>
+        <v>124258.3837145244</v>
       </c>
       <c r="E6">
-        <v>101923.4521199962</v>
+        <v>101925.1604740197</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10984.49438409729</v>
+        <v>10984.60647636427</v>
       </c>
       <c r="C7">
-        <v>22040.59410162596</v>
+        <v>22040.8603003524</v>
       </c>
       <c r="D7">
-        <v>24315.46640718524</v>
+        <v>24316.58526132198</v>
       </c>
       <c r="E7">
-        <v>26494.79899188094</v>
+        <v>26495.86891294193</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>810325.4609711046</v>
+        <v>810339.2016567425</v>
       </c>
       <c r="C9">
-        <v>1302693.765400807</v>
+        <v>1302722.97210362</v>
       </c>
       <c r="D9">
-        <v>1766895.429301083</v>
+        <v>1767235.459970791</v>
       </c>
       <c r="E9">
-        <v>2178879.533448599</v>
+        <v>2179084.738269533</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -558,13 +558,13 @@
         <v>869058.5042791282</v>
       </c>
       <c r="C12">
-        <v>1026488.819978358</v>
+        <v>1037605.050160827</v>
       </c>
       <c r="D12">
-        <v>921807.9964264584</v>
+        <v>929862.4735062823</v>
       </c>
       <c r="E12">
-        <v>712845.9476684948</v>
+        <v>713967.6212424268</v>
       </c>
     </row>
     <row r="13" spans="1:5">
